--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.2-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.2-2026-07-19.xlsx
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Founder (chat, 2026-07-19) — mock lookahead-v3 pending final approval</t>
+          <t>Founder — APPROVED 2026-07-19 (with mock lookahead-v3 FINAL)</t>
         </is>
       </c>
     </row>
